--- a/output/pdf_financials_xlsx/LEGY.xlsx
+++ b/output/pdf_financials_xlsx/LEGY.xlsx
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.005355</v>
+        <v>-0.005355</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.135262</v>
+        <v>-0.135262</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.858424</v>
+        <v>-0.858424</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.368127</v>
+        <v>-2.368127</v>
       </c>
     </row>
     <row r="17">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.005355</v>
+        <v>-0.005355</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.135262</v>
+        <v>-0.135262</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.858424</v>
+        <v>-0.858424</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.368127</v>
+        <v>-2.368127</v>
       </c>
     </row>
     <row r="21">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.005355</v>
+        <v>-0.005355</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.135262</v>
+        <v>-0.135262</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.858424</v>
+        <v>-0.858424</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.368127</v>
+        <v>-2.368127</v>
       </c>
     </row>
     <row r="24">
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.845388</v>
+        <v>-0.845388</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>7.803855</v>
+        <v>-7.803855</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>26.312522</v>
+        <v>-26.312522</v>
       </c>
     </row>
     <row r="27">
@@ -946,16 +946,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.005355</v>
+        <v>-0.005355</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.135262</v>
+        <v>-0.135262</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.858424</v>
+        <v>-0.858424</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.368127</v>
+        <v>-2.368127</v>
       </c>
     </row>
     <row r="28">
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.005355</v>
+        <v>-0.005355</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.135262</v>
+        <v>-0.135262</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.858424</v>
+        <v>-0.858424</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.368127</v>
+        <v>-2.368127</v>
       </c>
     </row>
     <row r="30">
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.115238</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.416385</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.6034080000000001</v>
       </c>
     </row>
     <row r="93">
@@ -3372,7 +3372,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4928,16 +4932,16 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.005355</v>
+        <v>-0.005355</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.135262</v>
+        <v>-0.135262</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.858424</v>
+        <v>-0.858424</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>2.368127</v>
+        <v>-2.368127</v>
       </c>
     </row>
     <row r="53">

--- a/output/pdf_financials_xlsx/LEGY.xlsx
+++ b/output/pdf_financials_xlsx/LEGY.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.005355</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.135262</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.125246</v>
+        <v>0.866465</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.404785</v>
+        <v>2.371298</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.005355</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.135262</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.125246</v>
+        <v>-0.866465</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.404785</v>
+        <v>-2.371298</v>
       </c>
     </row>
     <row r="12">
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.008041</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003171</v>
       </c>
     </row>
     <row r="13">
@@ -952,10 +952,10 @@
         <v>-0.135262</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.858424</v>
+        <v>-0.866465</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.368127</v>
+        <v>-2.371298</v>
       </c>
     </row>
     <row r="28">
@@ -990,10 +990,10 @@
         <v>-0.135262</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.858424</v>
+        <v>-0.866465</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.368127</v>
+        <v>-2.371298</v>
       </c>
     </row>
     <row r="30">
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.437784</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.525797</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.537357</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.494039</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.437784</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.525797</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.537357</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.494039</v>
       </c>
     </row>
     <row r="37">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.452784</v>
+        <v>0.015</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.527192</v>
+        <v>0.001395</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.569243</v>
+        <v>0.031886</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.538205</v>
+        <v>0.044166</v>
       </c>
     </row>
     <row r="49">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">

--- a/output/pdf_financials_xlsx/LEGY.xlsx
+++ b/output/pdf_financials_xlsx/LEGY.xlsx
@@ -550,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.125246</v>
+        <v>0.166856</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.404785</v>
+        <v>0.530785</v>
       </c>
     </row>
     <row r="8">
@@ -4634,7 +4634,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
